--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
